--- a/uploads/Planilha1.xlsx
+++ b/uploads/Planilha1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pax Primavera\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC692880-6F55-4081-BBCC-4994173BF45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66737BD3-A677-4BC8-B640-16FD6DADB4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{043B4702-F872-4250-B129-AF72C701923F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{95FC6CD8-1CF5-4F15-983A-6F4BC83036F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendas" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="392">
   <si>
     <t>AMAMBAI</t>
   </si>
@@ -199,6 +199,30 @@
     <t>RUA VICENTE SOARES  QD  LT  NUM 15 ENTRE O CANDIDO GARCIA E VICENTE SOARES VILA NOVA ANTONIO JOAO</t>
   </si>
   <si>
+    <t>TANIA APARECIDA VALENSUELA MEDINA</t>
+  </si>
+  <si>
+    <t>VENDAS DIGITAIS</t>
+  </si>
+  <si>
+    <t>RUA  DAS PRIMAVERAS QD  LT  NUM 08  POR DO SOL ANTONIO JOAO</t>
+  </si>
+  <si>
+    <t>ARAL MOREIRA</t>
+  </si>
+  <si>
+    <t>DANA REGINA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>MARLON DA SILVA LAURINDO</t>
+  </si>
+  <si>
+    <t>PLANO 3</t>
+  </si>
+  <si>
+    <t>RUA ANDRE BRITES DA SILVA QD  LT  NUM 36  IDELFONSO MONTEIRO ARAL MOREIRA</t>
+  </si>
+  <si>
     <t>CAARAPO</t>
   </si>
   <si>
@@ -232,6 +256,30 @@
     <t>RUA PROCÓPIO QD  LT  NUM 1080 CASA JARDIM APRAZIVEL CAARAPO</t>
   </si>
   <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>EDSON LOPES DA ROCHA</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>BOLETO CAIXA CASCAVEL</t>
+  </si>
+  <si>
+    <t>PADRAO BOLETO CAIXA CASCAVEL</t>
+  </si>
+  <si>
+    <t>EM VIDA</t>
+  </si>
+  <si>
+    <t>RUA RIO PAJEÚ QD  LT  NUM 182  BRASMADEIRA CASCAVEL</t>
+  </si>
+  <si>
+    <t>ANDREIA LOPES DA ROCHA</t>
+  </si>
+  <si>
     <t>DOURADINA</t>
   </si>
   <si>
@@ -307,6 +355,12 @@
     <t>RUA OSMAN AHAMAD GEBARA QD  LT  NUM 930  PARQUE ALVORADA DOURADOS</t>
   </si>
   <si>
+    <t>MARIA LUCILENE MAZARIM DA COSTA</t>
+  </si>
+  <si>
+    <t>RUA JOAO VICENTE FERREIRA QD  LT  NUM 6600 CASA JARDIM MARACANA DOURADOS</t>
+  </si>
+  <si>
     <t>ANTONIO MIGUEL ARAUJO LIMA</t>
   </si>
   <si>
@@ -337,18 +391,48 @@
     <t>RUA DOM JOAO VI QD  LT  NUM 1940  JARDIM PIRATININGA DOURADOS</t>
   </si>
   <si>
+    <t>ROSA MARIA VIEIRA FERNANDES</t>
+  </si>
+  <si>
+    <t>NATALIA ZAGHI VITOR</t>
+  </si>
+  <si>
+    <t>RUA OLINDA PIRES DE ALMEIDA QD  LT  NUM 3065 CASA  VILA PLANALTO DOURADOS</t>
+  </si>
+  <si>
     <t>VANDERSON APARECIDO DE SOUZA</t>
   </si>
   <si>
-    <t>NATALIA ZAGHI VITOR</t>
-  </si>
-  <si>
     <t>BOLETO BANCARIO REGIAO 04</t>
   </si>
   <si>
     <t>RUA FERNANDO FERRARI QD  LT  NUM 827 CASA  VILA INDUSTRIAL DOURADOS</t>
   </si>
   <si>
+    <t>MARISTELA CANISSO VALESE</t>
+  </si>
+  <si>
+    <t>TAINARA RIBEIRO BRAGA</t>
+  </si>
+  <si>
+    <t>RUA HILDA BERGO DUARTE QD  LT  NUM 1755  VILA PLANALTO DOURADOS</t>
+  </si>
+  <si>
+    <t>ELIZEU OLIVEIRA DIAS</t>
+  </si>
+  <si>
+    <t>RUA SEIJI NISHIOKA QD  LT  NUM 100 CASA DOS FUNDOS  ALTOS DO INDAIA DOURADOS</t>
+  </si>
+  <si>
+    <t>MARIA NILZA ALMINO</t>
+  </si>
+  <si>
+    <t>BOLETO BANCARIO REGIAO 03</t>
+  </si>
+  <si>
+    <t>RUA CUIABA QD  LT  NUM 2778  CENTRO DOURADOS</t>
+  </si>
+  <si>
     <t>HALCIONE MOREIRA VINCIGUERA</t>
   </si>
   <si>
@@ -376,15 +460,39 @@
     <t>RUA ENTRE RIOS  QD  LT  NUM 2085  DISTRITO DE ITAHUM DOURADOS</t>
   </si>
   <si>
+    <t>WANIA ALINE CHAVES</t>
+  </si>
+  <si>
+    <t>RUA ALVICIO MARTINS VIANA QD  LT  NUM 2310  IZIDRO PEDROSO DOURADOS</t>
+  </si>
+  <si>
+    <t>MARCELO MARQUES DE FREITAS SILVA</t>
+  </si>
+  <si>
+    <t>RUA CLOVIS CERZOSIMO DE SOUZA QD  LT  NUM 5185  VILA ROSA DOURADOS</t>
+  </si>
+  <si>
+    <t>SIMONE EMIDIO ONOFRE</t>
+  </si>
+  <si>
+    <t>RUA RANGEL TORRES QD  LT  NUM 2115 CASA JARDIM DOS ESTADOS DOURADOS</t>
+  </si>
+  <si>
+    <t>NEDINA FERREIRA CORREA</t>
+  </si>
+  <si>
+    <t>RUA  KESAYOSHE ANZE QD  LT  NUM 395  ALTOS DO INDAIA DOURADOS</t>
+  </si>
+  <si>
+    <t>MONIQUE FIORAVANTI SANSAO BAZAN</t>
+  </si>
+  <si>
+    <t>RUA AVENIDA WEIMAR TORRES QD  LT  NUM 1964 CASA CENTRO DOURADOS</t>
+  </si>
+  <si>
     <t>GILBERTO DOS SANTOS</t>
   </si>
   <si>
-    <t>VENDAS DIGITAIS</t>
-  </si>
-  <si>
-    <t>BOLETO BANCARIO REGIAO 03</t>
-  </si>
-  <si>
     <t>RUA RUA PANCHO TORRACA QD  LT  NUM 342  VILA CACHOEIRINHA DOURADOS</t>
   </si>
   <si>
@@ -394,6 +502,12 @@
     <t>RUA PAULO TEIXEIRA DE ALMEIDA QD  LT  NUM 765  PARQUE DAS NACOES 02 DOURADOS</t>
   </si>
   <si>
+    <t>MARY LUCI SANTOS DE SOUZA</t>
+  </si>
+  <si>
+    <t>RUA JURITI QD  LT  NUM 1330 CASA ESPLANADA DOURADOS</t>
+  </si>
+  <si>
     <t>PRISCILA MELLO DOS SANTOS</t>
   </si>
   <si>
@@ -460,12 +574,27 @@
     <t>IGUATEMI</t>
   </si>
   <si>
+    <t>RENATA KERLE GONCALVES GARCIA</t>
+  </si>
+  <si>
+    <t>EMELY SARA NOGUEIRA CAVALCANTE</t>
+  </si>
+  <si>
+    <t>BOLETO BANCARIO IGUATEMI</t>
+  </si>
+  <si>
+    <t>RUA SANTA CATARINA  QD  LT  NUM 195  SANTA JALMIRA IGUATEMI</t>
+  </si>
+  <si>
+    <t>DANIELI OLIVEIRA LIMA</t>
+  </si>
+  <si>
+    <t>RUA LINDOLFO MARTINS FARIAS QD  LT  NUM 308 CASA VILA NOVA ESPERANCA IGUATEMI</t>
+  </si>
+  <si>
     <t>MARGARETE DA FONSECA GONCALVES</t>
   </si>
   <si>
-    <t>BOLETO BANCARIO IGUATEMI</t>
-  </si>
-  <si>
     <t>RUA RUA MUNDO NOVO QD  LT  NUM 33  VILA NOVA IGUATEMI</t>
   </si>
   <si>
@@ -502,6 +631,21 @@
     <t>RUA JUSCELINO K. DE OLIVEIRA QD  LT  NUM 1  CENTRO ITAPORA</t>
   </si>
   <si>
+    <t>ITAQUIRAI</t>
+  </si>
+  <si>
+    <t>LUCIANA OLIVEIRA DOS SANTOS PADUINA</t>
+  </si>
+  <si>
+    <t>CARINE FERNANDA DE MATOS PUTON</t>
+  </si>
+  <si>
+    <t>COB. PARCELAS</t>
+  </si>
+  <si>
+    <t>RUA VALE AZUL QD  LT  NUM 501  NOVA ESPERANCA ITAQUIRAI</t>
+  </si>
+  <si>
     <t>JUTI</t>
   </si>
   <si>
@@ -619,42 +763,69 @@
     <t>RUA MACOQUEIRO QD  LT  NUM 252  RESIDENCIAL IPE NAVIRAI</t>
   </si>
   <si>
+    <t>NARCISO CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>GRANJA FAZENDA IPUITA QD  LT  NUM S/N  ZONA RURAL NAVIRAI</t>
+  </si>
+  <si>
     <t>NOVA ALVORADA</t>
   </si>
   <si>
+    <t>HEMERSON CABRAL VEGA</t>
+  </si>
+  <si>
+    <t>EDSON DE SOUZA MATOS</t>
+  </si>
+  <si>
+    <t>COB.BOLETOS</t>
+  </si>
+  <si>
+    <t>PAX PLANO LUXO 3</t>
+  </si>
+  <si>
+    <t>RUA TERESA LEMES  DE OLIVEIRA QD  LT  NUM 278  JAIME DE MEDEIROS NOVA ALVORADA DO SUL</t>
+  </si>
+  <si>
     <t>THAISY MENDES DA CONCEICAO</t>
   </si>
   <si>
-    <t>COB.BOLETOS</t>
-  </si>
-  <si>
-    <t>PAX PLANO LUXO 3</t>
-  </si>
-  <si>
     <t>RUA EUSTAQUIO VARGAS QD  LT  NUM 2634  VILA MARIA DE LOURDES NOVA ALVORADA DO SUL</t>
   </si>
   <si>
     <t>NOVA IGUACU</t>
   </si>
   <si>
+    <t>QUELZA CRISTINA DE LEMOS COSTA</t>
+  </si>
+  <si>
+    <t>TALITA JUNIA DA CONCEICAO SILVA</t>
+  </si>
+  <si>
+    <t>PLANO II</t>
+  </si>
+  <si>
+    <t>COBRADOR BOLETO BANCARIO</t>
+  </si>
+  <si>
+    <t>126,5</t>
+  </si>
+  <si>
+    <t>RUA KELER QD  LT  NUM 61  JARDIM ALVORADA NOVA IGUACU</t>
+  </si>
+  <si>
     <t>IZABEL CRISTINA FERREIRA ALVES</t>
   </si>
   <si>
-    <t>TALITA JUNIA DA CONCEICAO SILVA</t>
-  </si>
-  <si>
-    <t>PLANO II</t>
-  </si>
-  <si>
-    <t>COBRADOR BOLETO BANCARIO</t>
-  </si>
-  <si>
-    <t>126,5</t>
-  </si>
-  <si>
     <t>RUA DOUTOR RIDEL QD  LT  NUM 557 CASA 01 AMBAI NOVA IGUACU</t>
   </si>
   <si>
+    <t>SARAH DE SOUZA REIS</t>
+  </si>
+  <si>
+    <t>RUA REGINA QD  LT  NUM 300 COND. LARANJEIRAS CABUCU NOVA IGUACU</t>
+  </si>
+  <si>
     <t>EDILSON ABILIO DA SILVA</t>
   </si>
   <si>
@@ -664,13 +835,64 @@
     <t>ESTRADA MORRO AGUDO QD A LT  NUM 5  PALHADA NOVA IGUACU</t>
   </si>
   <si>
-    <t>QUELZA CRISTINA DE LEMOS COSTA</t>
-  </si>
-  <si>
-    <t>PLANO III</t>
-  </si>
-  <si>
-    <t>RUA KELER QD  LT  NUM 61  JARDIM ALVORADA NOVA IGUACU</t>
+    <t>ROSANGELA BAPTISTA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>RUA DORNIL QD  LT  NUM 06 CASA CACUIA NOVA IGUACU</t>
+  </si>
+  <si>
+    <t>EDILENE CORREIA DE LIRA</t>
+  </si>
+  <si>
+    <t>RUA WASHINGTON LUIS QD  LT  NUM 608 CASA JARDIM PERNAMBUCO NOVA IGUACU</t>
+  </si>
+  <si>
+    <t>PJC</t>
+  </si>
+  <si>
+    <t>ISABEL VEGA RUIZ</t>
+  </si>
+  <si>
+    <t>DIANA ELIZABETH FERREIRA PALACIOS</t>
+  </si>
+  <si>
+    <t>COB.JUAN JAVIER ALMADA ARMOA</t>
+  </si>
+  <si>
+    <t>PLANO BASICO</t>
+  </si>
+  <si>
+    <t>DIA 10</t>
+  </si>
+  <si>
+    <t>RUA TOLEDO E/ESTRELLA QD  LT  NUM   SAN JUAN NEUMAN PJC</t>
+  </si>
+  <si>
+    <t>EVA CELIA DELGADO BRITEZ</t>
+  </si>
+  <si>
+    <t>VEND.ANA BENITEZ</t>
+  </si>
+  <si>
+    <t>COB.EFRAIN</t>
+  </si>
+  <si>
+    <t>RUA DR FRANCIA Y COLON C/ALBERDI QD  LT  NUM 88  CENTRO PJC</t>
+  </si>
+  <si>
+    <t>SARA ELENA LESME MARQUES</t>
+  </si>
+  <si>
+    <t>RUA NATALICIO TALAVERA Y PERPETUO SOCORRO QD  LT  NUM 1060  CENTRO PJC</t>
+  </si>
+  <si>
+    <t>BETTY ZUNILDA SALINAS</t>
+  </si>
+  <si>
+    <t>DIA 27</t>
+  </si>
+  <si>
+    <t>RUA NATALICIO TALAVERA E/ALBERDI QD  LT  NUM 773  MARISCAL ESTIGARRIBIA PJC</t>
   </si>
   <si>
     <t>PONTA PORA COBRANCA</t>
@@ -718,6 +940,15 @@
     <t>RUA NICARAGUA  QD  LT  NUM 356  ESTORIL PONTA PORA</t>
   </si>
   <si>
+    <t>THAINARA BIANCA AJALA ZABALLOS</t>
+  </si>
+  <si>
+    <t>MAYRA ALMEIDA SILVA</t>
+  </si>
+  <si>
+    <t>RUA ALCIDES LOUREIRO QD  LT  NUM 76  PARQUE DOS IPES 02 PONTA PORA</t>
+  </si>
+  <si>
     <t>MATEUS NAPOLEAO ANDRE</t>
   </si>
   <si>
@@ -757,6 +988,15 @@
     <t>RUA FELICIANA MARIA FRANCISCA QD  LT  NUM 1634  ESTORIL 1 RIBAS DO RIO PARDO</t>
   </si>
   <si>
+    <t>IZABEL DA CONCEICAO DA SILVA</t>
+  </si>
+  <si>
+    <t>RONIE MEDEIROS</t>
+  </si>
+  <si>
+    <t>RUA ELISEU SANCHES DA SILVA QD  LT  NUM 1011  SANTO ANDRE RIBAS DO RIO PARDO</t>
+  </si>
+  <si>
     <t>RIO BRILHANTE</t>
   </si>
   <si>
@@ -769,9 +1009,6 @@
     <t>COB.REGIELI DE SOUZA SOARES</t>
   </si>
   <si>
-    <t>DIA 10</t>
-  </si>
-  <si>
     <t>RUA LINA MOURA MUNIZ QD  LT  NUM 1127  MANOEL DAS NEVES RIO BRILHANTE</t>
   </si>
   <si>
@@ -814,6 +1051,12 @@
     <t>RUA GOVERNADOR FERNANDO CORREA DA COSTA QD  LT  NUM 1387  VILA PROGRESSO RIO BRILHANTE</t>
   </si>
   <si>
+    <t>EVA APARECIDA CONDE LIMA</t>
+  </si>
+  <si>
+    <t>RUA MARIO SEGUNDO PIRES VIDEIRA QD 374 LT 2 NUM S/N  PRO MORADIA 15 RIO BRILHANTE</t>
+  </si>
+  <si>
     <t>JOSIANE MARTINS MENDONCA LOPES</t>
   </si>
   <si>
@@ -899,6 +1142,12 @@
   </si>
   <si>
     <t>RUA GUAIBA QD  LT  NUM 474  NOVA ALIANÇA L - ID 1 SORRISO</t>
+  </si>
+  <si>
+    <t>ROSANA RESENDE</t>
+  </si>
+  <si>
+    <t>TRAVESSA HAVAI QD  LT  NUM 646  JARDIM TROPICAL - ID 1 SORRISO</t>
   </si>
   <si>
     <t>UNIDADE</t>
@@ -1322,8 +1571,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207E7631-2609-49D1-8393-F3EF4E8E394A}">
-  <dimension ref="A1:U81"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9851872D-0A3A-4F90-8E19-AEE7BD3436FD}">
+  <dimension ref="A1:U112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -1335,7 +1584,7 @@
     <col min="7" max="7" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -1351,67 +1600,67 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>288</v>
+        <v>371</v>
       </c>
       <c r="B1" t="s">
-        <v>289</v>
+        <v>372</v>
       </c>
       <c r="C1" t="s">
-        <v>290</v>
+        <v>373</v>
       </c>
       <c r="D1" t="s">
-        <v>291</v>
+        <v>374</v>
       </c>
       <c r="E1" t="s">
-        <v>292</v>
+        <v>375</v>
       </c>
       <c r="F1" t="s">
-        <v>293</v>
+        <v>376</v>
       </c>
       <c r="G1" t="s">
-        <v>294</v>
+        <v>377</v>
       </c>
       <c r="H1" t="s">
-        <v>295</v>
+        <v>378</v>
       </c>
       <c r="I1" t="s">
-        <v>296</v>
+        <v>379</v>
       </c>
       <c r="J1" t="s">
-        <v>297</v>
+        <v>380</v>
       </c>
       <c r="K1" t="s">
-        <v>298</v>
+        <v>381</v>
       </c>
       <c r="L1" t="s">
-        <v>299</v>
+        <v>382</v>
       </c>
       <c r="M1" t="s">
-        <v>300</v>
+        <v>383</v>
       </c>
       <c r="N1" t="s">
-        <v>301</v>
+        <v>384</v>
       </c>
       <c r="O1" t="s">
-        <v>302</v>
+        <v>385</v>
       </c>
       <c r="P1" t="s">
-        <v>303</v>
+        <v>386</v>
       </c>
       <c r="Q1" t="s">
-        <v>304</v>
+        <v>387</v>
       </c>
       <c r="R1" t="s">
-        <v>305</v>
+        <v>388</v>
       </c>
       <c r="S1" t="s">
-        <v>306</v>
+        <v>389</v>
       </c>
       <c r="T1" t="s">
-        <v>307</v>
+        <v>390</v>
       </c>
       <c r="U1" t="s">
-        <v>308</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -1509,22 +1758,28 @@
         <v>9</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
-      </c>
-      <c r="L3" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L3" s="2">
+        <v>45783</v>
+      </c>
       <c r="M3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
+      <c r="O3" s="2">
+        <v>45783</v>
+      </c>
+      <c r="P3" s="2">
+        <v>45753</v>
+      </c>
       <c r="Q3" s="1">
         <v>0</v>
       </c>
       <c r="R3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="1"/>
       <c r="T3" s="1">
@@ -1989,22 +2244,28 @@
         <v>30</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L11" s="2">
+        <v>45814</v>
+      </c>
       <c r="M11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
+      <c r="O11" s="2">
+        <v>45814</v>
+      </c>
+      <c r="P11" s="2">
+        <v>45753</v>
+      </c>
       <c r="Q11" s="1">
         <v>0</v>
       </c>
       <c r="R11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1">
@@ -2415,103 +2676,97 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="1">
+        <v>19886</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="1">
-        <v>31176</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="2">
-        <v>45694</v>
-      </c>
-      <c r="E19" s="2">
-        <v>45694</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="G19" s="1" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I19" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="K19" s="1">
-        <v>50</v>
-      </c>
-      <c r="L19" s="2">
-        <v>45694</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O19" s="2">
-        <v>45694</v>
-      </c>
-      <c r="P19" s="2">
-        <v>45694</v>
-      </c>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
       <c r="Q19" s="1">
         <v>0</v>
       </c>
       <c r="R19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1">
         <v>0</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B20" s="1">
-        <v>31177</v>
+        <v>20609</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45783</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="2">
-        <v>45722</v>
-      </c>
-      <c r="E20" s="2">
-        <v>45722</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="I20" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="K20" s="1">
         <v>50</v>
       </c>
       <c r="L20" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>5</v>
@@ -2520,10 +2775,10 @@
         <v>6</v>
       </c>
       <c r="O20" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="P20" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="Q20" s="1">
         <v>0</v>
@@ -2541,40 +2796,40 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B21" s="1">
-        <v>31178</v>
+        <v>31176</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="E21" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I21" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K21" s="1">
         <v>50</v>
       </c>
       <c r="L21" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>5</v>
@@ -2583,10 +2838,10 @@
         <v>6</v>
       </c>
       <c r="O21" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="P21" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="Q21" s="1">
         <v>0</v>
@@ -2599,102 +2854,108 @@
         <v>0</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="1">
+        <v>31177</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="2">
+        <v>45722</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45722</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="1">
-        <v>24072</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="H22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="1">
+        <v>10</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="2">
-        <v>45753</v>
-      </c>
-      <c r="E22" s="2">
-        <v>45753</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" s="1">
-        <v>4</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="K22" s="1">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L22" s="2">
+        <v>45722</v>
+      </c>
       <c r="M22" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
+      <c r="O22" s="2">
+        <v>45722</v>
+      </c>
+      <c r="P22" s="2">
+        <v>45722</v>
+      </c>
       <c r="Q22" s="1">
         <v>0</v>
       </c>
       <c r="R22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1">
         <v>0</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B23" s="1">
-        <v>102544</v>
+        <v>31178</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D23" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="E23" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="I23" s="1">
         <v>10</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K23" s="1">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="L23" s="2">
-        <v>45722</v>
+        <v>45753</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>5</v>
@@ -2703,10 +2964,10 @@
         <v>6</v>
       </c>
       <c r="O23" s="2">
-        <v>45722</v>
+        <v>45753</v>
       </c>
       <c r="P23" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="Q23" s="1">
         <v>0</v>
@@ -2719,58 +2980,52 @@
         <v>0</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B24" s="1">
-        <v>102545</v>
+        <v>13571</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" s="1">
+        <v>12</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="2">
-        <v>45694</v>
-      </c>
-      <c r="E24" s="2">
-        <v>45694</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="1">
-        <v>5</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K24" s="1">
-        <v>50</v>
-      </c>
-      <c r="L24" s="2">
-        <v>45722</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="N24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O24" s="2">
-        <v>45722</v>
-      </c>
-      <c r="P24" s="2">
-        <v>45694</v>
-      </c>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
       <c r="Q24" s="1">
         <v>0</v>
       </c>
@@ -2782,58 +3037,52 @@
         <v>0</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B25" s="1">
-        <v>102552</v>
+        <v>13570</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D25" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="E25" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I25" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K25" s="1">
-        <v>160</v>
-      </c>
-      <c r="L25" s="2">
-        <v>45753</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O25" s="2">
-        <v>45753</v>
-      </c>
-      <c r="P25" s="2">
-        <v>45722</v>
-      </c>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
       <c r="Q25" s="1">
         <v>0</v>
       </c>
@@ -2845,63 +3094,57 @@
         <v>0</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B26" s="1">
-        <v>102547</v>
+        <v>24072</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="2">
+        <v>45753</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45753</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="2">
-        <v>45722</v>
-      </c>
-      <c r="E26" s="2">
-        <v>45722</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1">
         <v>4</v>
       </c>
-      <c r="I26" s="1">
-        <v>15</v>
-      </c>
       <c r="J26" s="1" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
       </c>
-      <c r="L26" s="2">
-        <v>45753</v>
-      </c>
+      <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O26" s="2">
-        <v>45753</v>
-      </c>
-      <c r="P26" s="2">
-        <v>45722</v>
-      </c>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
       <c r="Q26" s="1">
         <v>0</v>
       </c>
       <c r="R26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="1"/>
       <c r="T26" s="1">
@@ -2913,40 +3156,40 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B27" s="1">
-        <v>102555</v>
+        <v>102544</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D27" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="E27" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="I27" s="1">
         <v>10</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K27" s="1">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="L27" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>5</v>
@@ -2955,10 +3198,10 @@
         <v>6</v>
       </c>
       <c r="O27" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="P27" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="Q27" s="1">
         <v>0</v>
@@ -2971,45 +3214,45 @@
         <v>0</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B28" s="1">
-        <v>102554</v>
+        <v>102545</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D28" s="2">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="E28" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I28" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K28" s="1">
         <v>50</v>
       </c>
       <c r="L28" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>5</v>
@@ -3018,10 +3261,10 @@
         <v>6</v>
       </c>
       <c r="O28" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="P28" s="2">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="Q28" s="1">
         <v>0</v>
@@ -3034,18 +3277,18 @@
         <v>0</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B29" s="1">
-        <v>102550</v>
+        <v>102552</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D29" s="2">
         <v>45722</v>
@@ -3054,19 +3297,19 @@
         <v>45753</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="I29" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K29" s="1">
         <v>160</v>
@@ -3097,18 +3340,18 @@
         <v>0</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B30" s="1">
-        <v>102549</v>
+        <v>102547</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D30" s="2">
         <v>45722</v>
@@ -3120,16 +3363,16 @@
         <v>98</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
@@ -3160,45 +3403,45 @@
         <v>0</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B31" s="1">
-        <v>102559</v>
+        <v>102555</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D31" s="2">
-        <v>45783</v>
+        <v>45753</v>
       </c>
       <c r="E31" s="2">
-        <v>45783</v>
+        <v>45753</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="I31" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K31" s="1">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="L31" s="2">
-        <v>45783</v>
+        <v>45753</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>5</v>
@@ -3207,10 +3450,10 @@
         <v>6</v>
       </c>
       <c r="O31" s="2">
-        <v>45783</v>
+        <v>45753</v>
       </c>
       <c r="P31" s="2">
-        <v>45783</v>
+        <v>45753</v>
       </c>
       <c r="Q31" s="1">
         <v>0</v>
@@ -3223,30 +3466,30 @@
         <v>0</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B32" s="1">
-        <v>102548</v>
+        <v>102567</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45783</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="D32" s="2">
-        <v>45722</v>
-      </c>
-      <c r="E32" s="2">
-        <v>45722</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>4</v>
@@ -3255,13 +3498,13 @@
         <v>10</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K32" s="1">
         <v>50</v>
       </c>
       <c r="L32" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>5</v>
@@ -3270,10 +3513,10 @@
         <v>6</v>
       </c>
       <c r="O32" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="P32" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="Q32" s="1">
         <v>0</v>
@@ -3286,216 +3529,234 @@
         <v>0</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B33" s="1">
-        <v>102556</v>
+        <v>102554</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D33" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="E33" s="2">
         <v>45753</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I33" s="1">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L33" s="2">
+        <v>45753</v>
+      </c>
       <c r="M33" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
+      <c r="O33" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P33" s="2">
+        <v>45722</v>
+      </c>
       <c r="Q33" s="1">
         <v>0</v>
       </c>
       <c r="R33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" s="1"/>
       <c r="T33" s="1">
         <v>0</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B34" s="1">
-        <v>102557</v>
+        <v>102550</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D34" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="E34" s="2">
         <v>45753</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="I34" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="K34" s="1">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="L34" s="2">
+        <v>45753</v>
+      </c>
       <c r="M34" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
+      <c r="O34" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P34" s="2">
+        <v>45722</v>
+      </c>
       <c r="Q34" s="1">
         <v>0</v>
       </c>
       <c r="R34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" s="1"/>
       <c r="T34" s="1">
         <v>0</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B35" s="1">
-        <v>102558</v>
+        <v>102549</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D35" s="2">
-        <v>45783</v>
+        <v>45722</v>
       </c>
       <c r="E35" s="2">
-        <v>45783</v>
+        <v>45722</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I35" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
       </c>
-      <c r="L35" s="1"/>
+      <c r="L35" s="2">
+        <v>45753</v>
+      </c>
       <c r="M35" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
+      <c r="O35" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P35" s="2">
+        <v>45722</v>
+      </c>
       <c r="Q35" s="1">
         <v>0</v>
       </c>
       <c r="R35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1">
         <v>0</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B36" s="1">
-        <v>102551</v>
+        <v>102563</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D36" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="E36" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="I36" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K36" s="1">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="L36" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>5</v>
@@ -3504,10 +3765,10 @@
         <v>6</v>
       </c>
       <c r="O36" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="P36" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="Q36" s="1">
         <v>0</v>
@@ -3520,18 +3781,18 @@
         <v>0</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B37" s="1">
-        <v>102562</v>
+        <v>102559</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D37" s="2">
         <v>45783</v>
@@ -3540,124 +3801,136 @@
         <v>45783</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="I37" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="K37" s="1">
-        <v>0</v>
-      </c>
-      <c r="L37" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="L37" s="2">
+        <v>45783</v>
+      </c>
       <c r="M37" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
+      <c r="O37" s="2">
+        <v>45783</v>
+      </c>
+      <c r="P37" s="2">
+        <v>45783</v>
+      </c>
       <c r="Q37" s="1">
         <v>0</v>
       </c>
       <c r="R37" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1">
         <v>0</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B38" s="1">
-        <v>102561</v>
+        <v>102570</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D38" s="2">
         <v>45783</v>
       </c>
       <c r="E38" s="2">
-        <v>45783</v>
+        <v>45814</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="I38" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K38" s="1">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="L38" s="2">
+        <v>45814</v>
+      </c>
       <c r="M38" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
+      <c r="O38" s="2">
+        <v>45814</v>
+      </c>
+      <c r="P38" s="2">
+        <v>45783</v>
+      </c>
       <c r="Q38" s="1">
         <v>0</v>
       </c>
       <c r="R38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1">
         <v>0</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B39" s="1">
-        <v>102560</v>
+        <v>102571</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D39" s="2">
         <v>45783</v>
       </c>
       <c r="E39" s="2">
-        <v>45783</v>
+        <v>45814</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>4</v>
@@ -3666,70 +3939,76 @@
         <v>10</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K39" s="1">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L39" s="2">
+        <v>45814</v>
+      </c>
       <c r="M39" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
+      <c r="O39" s="2">
+        <v>45814</v>
+      </c>
+      <c r="P39" s="2">
+        <v>45783</v>
+      </c>
       <c r="Q39" s="1">
         <v>0</v>
       </c>
       <c r="R39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1">
         <v>0</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B40" s="1">
-        <v>102539</v>
+        <v>102568</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D40" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="E40" s="2">
-        <v>45694</v>
+        <v>45814</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="I40" s="1">
         <v>10</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K40" s="1">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="L40" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>5</v>
@@ -3738,10 +4017,10 @@
         <v>6</v>
       </c>
       <c r="O40" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="P40" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="Q40" s="1">
         <v>0</v>
@@ -3754,57 +4033,57 @@
         <v>0</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B41" s="1">
-        <v>102542</v>
+        <v>102548</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D41" s="2">
-        <v>45694</v>
+        <v>45722</v>
       </c>
       <c r="E41" s="2">
-        <v>45694</v>
+        <v>45722</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="I41" s="1">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K41" s="1">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="L41" s="2">
+        <v>45753</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O41" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P41" s="2">
         <v>45722</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O41" s="2">
-        <v>45722</v>
-      </c>
-      <c r="P41" s="2">
-        <v>45694</v>
       </c>
       <c r="Q41" s="1">
         <v>0</v>
@@ -3817,45 +4096,45 @@
         <v>0</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="B42" s="1">
-        <v>3673</v>
+        <v>102556</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D42" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="E42" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="I42" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="K42" s="1">
         <v>50</v>
       </c>
       <c r="L42" s="2">
-        <v>45694</v>
+        <v>45814</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>5</v>
@@ -3864,10 +4143,10 @@
         <v>6</v>
       </c>
       <c r="O42" s="2">
-        <v>45694</v>
+        <v>45814</v>
       </c>
       <c r="P42" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="Q42" s="1">
         <v>0</v>
@@ -3880,45 +4159,45 @@
         <v>0</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="B43" s="1">
-        <v>9992</v>
+        <v>102557</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D43" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="E43" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>138</v>
+        <v>4</v>
       </c>
       <c r="I43" s="1">
         <v>10</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="K43" s="1">
         <v>50</v>
       </c>
       <c r="L43" s="2">
-        <v>45694</v>
+        <v>45814</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>5</v>
@@ -3927,10 +4206,10 @@
         <v>6</v>
       </c>
       <c r="O43" s="2">
-        <v>45694</v>
+        <v>45814</v>
       </c>
       <c r="P43" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="Q43" s="1">
         <v>0</v>
@@ -3943,45 +4222,45 @@
         <v>0</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="B44" s="1">
-        <v>5303</v>
+        <v>102558</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D44" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="E44" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="K44" s="1">
         <v>50</v>
       </c>
       <c r="L44" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>5</v>
@@ -3990,10 +4269,10 @@
         <v>6</v>
       </c>
       <c r="O44" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="P44" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="Q44" s="1">
         <v>0</v>
@@ -4006,102 +4285,108 @@
         <v>0</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="B45" s="1">
-        <v>5301</v>
+        <v>102566</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D45" s="2">
-        <v>45722</v>
+        <v>45753</v>
       </c>
       <c r="E45" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="I45" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="K45" s="1">
-        <v>0</v>
-      </c>
-      <c r="L45" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="L45" s="2">
+        <v>45814</v>
+      </c>
       <c r="M45" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
+      <c r="O45" s="2">
+        <v>45814</v>
+      </c>
+      <c r="P45" s="2">
+        <v>45753</v>
+      </c>
       <c r="Q45" s="1">
         <v>0</v>
       </c>
       <c r="R45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" s="1"/>
       <c r="T45" s="1">
         <v>0</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="B46" s="1">
-        <v>31896</v>
+        <v>102572</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D46" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="E46" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>148</v>
+        <v>55</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="I46" s="1">
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="K46" s="1">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="L46" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>5</v>
@@ -4110,10 +4395,10 @@
         <v>6</v>
       </c>
       <c r="O46" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="P46" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="Q46" s="1">
         <v>0</v>
@@ -4126,45 +4411,45 @@
         <v>0</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="B47" s="1">
-        <v>31897</v>
+        <v>102564</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D47" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="E47" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="I47" s="1">
         <v>10</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="K47" s="1">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="L47" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>5</v>
@@ -4173,10 +4458,10 @@
         <v>6</v>
       </c>
       <c r="O47" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="P47" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="Q47" s="1">
         <v>0</v>
@@ -4189,102 +4474,108 @@
         <v>0</v>
       </c>
       <c r="U47" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c r="B48" s="1">
-        <v>24402</v>
+        <v>102574</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D48" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="E48" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="I48" s="1">
         <v>10</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="K48" s="1">
-        <v>0</v>
-      </c>
-      <c r="L48" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="L48" s="2">
+        <v>45814</v>
+      </c>
       <c r="M48" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
+      <c r="O48" s="2">
+        <v>45814</v>
+      </c>
+      <c r="P48" s="2">
+        <v>45783</v>
+      </c>
       <c r="Q48" s="1">
         <v>0</v>
       </c>
       <c r="R48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1">
         <v>0</v>
       </c>
       <c r="U48" s="1" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="B49" s="1">
-        <v>26849</v>
+        <v>102565</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D49" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="E49" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>163</v>
+        <v>55</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
       <c r="I49" s="1">
         <v>10</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="K49" s="1">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="L49" s="2">
-        <v>45694</v>
+        <v>45814</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>5</v>
@@ -4293,10 +4584,10 @@
         <v>6</v>
       </c>
       <c r="O49" s="2">
-        <v>45694</v>
+        <v>45814</v>
       </c>
       <c r="P49" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="Q49" s="1">
         <v>0</v>
@@ -4309,18 +4600,18 @@
         <v>0</v>
       </c>
       <c r="U49" s="1" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="B50" s="1">
-        <v>7299</v>
+        <v>102551</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="D50" s="2">
         <v>45722</v>
@@ -4329,22 +4620,22 @@
         <v>45753</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>169</v>
+        <v>55</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>138</v>
+        <v>4</v>
       </c>
       <c r="I50" s="1">
         <v>10</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>171</v>
+        <v>95</v>
+      </c>
+      <c r="K50" s="1">
+        <v>50</v>
       </c>
       <c r="L50" s="2">
         <v>45753</v>
@@ -4372,45 +4663,45 @@
         <v>0</v>
       </c>
       <c r="U50" s="1" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="B51" s="1">
-        <v>7298</v>
+        <v>102562</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="D51" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="E51" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>174</v>
+        <v>55</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>176</v>
+        <v>4</v>
       </c>
       <c r="I51" s="1">
         <v>10</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="L51" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>5</v>
@@ -4419,63 +4710,61 @@
         <v>6</v>
       </c>
       <c r="O51" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="P51" s="2">
-        <v>45938</v>
+        <v>45783</v>
       </c>
       <c r="Q51" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R51" s="1">
         <v>0</v>
       </c>
-      <c r="S51" s="2">
-        <v>45722</v>
-      </c>
-      <c r="T51" s="1" t="s">
-        <v>177</v>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1">
+        <v>0</v>
       </c>
       <c r="U51" s="1" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="B52" s="1">
-        <v>7300</v>
+        <v>102573</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="D52" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="E52" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>181</v>
+        <v>94</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>176</v>
+        <v>4</v>
       </c>
       <c r="I52" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="K52" s="1">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="L52" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>5</v>
@@ -4484,10 +4773,10 @@
         <v>6</v>
       </c>
       <c r="O52" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="P52" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="Q52" s="1">
         <v>0</v>
@@ -4500,18 +4789,18 @@
         <v>0</v>
       </c>
       <c r="U52" s="1" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="B53" s="1">
-        <v>7301</v>
+        <v>102561</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="D53" s="2">
         <v>45783</v>
@@ -4520,25 +4809,25 @@
         <v>45783</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>176</v>
+        <v>4</v>
       </c>
       <c r="I53" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>177</v>
+        <v>95</v>
+      </c>
+      <c r="K53" s="1">
+        <v>50</v>
       </c>
       <c r="L53" s="2">
-        <v>45783</v>
+        <v>45814</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>5</v>
@@ -4547,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="O53" s="2">
-        <v>45783</v>
+        <v>45814</v>
       </c>
       <c r="P53" s="2">
         <v>45783</v>
@@ -4563,30 +4852,30 @@
         <v>0</v>
       </c>
       <c r="U53" s="1" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>186</v>
+        <v>87</v>
       </c>
       <c r="B54" s="1">
-        <v>13835</v>
+        <v>102560</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D54" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="E54" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>4</v>
@@ -4595,13 +4884,13 @@
         <v>10</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>189</v>
+        <v>95</v>
       </c>
       <c r="K54" s="1">
         <v>50</v>
       </c>
       <c r="L54" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>5</v>
@@ -4610,10 +4899,10 @@
         <v>6</v>
       </c>
       <c r="O54" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="P54" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="Q54" s="1">
         <v>0</v>
@@ -4626,45 +4915,45 @@
         <v>0</v>
       </c>
       <c r="U54" s="1" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>186</v>
+        <v>87</v>
       </c>
       <c r="B55" s="1">
-        <v>13836</v>
+        <v>102539</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="D55" s="2">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="E55" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="I55" s="1">
         <v>10</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>192</v>
+        <v>95</v>
       </c>
       <c r="K55" s="1">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="L55" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>5</v>
@@ -4673,10 +4962,10 @@
         <v>6</v>
       </c>
       <c r="O55" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="P55" s="2">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="Q55" s="1">
         <v>0</v>
@@ -4689,102 +4978,108 @@
         <v>0</v>
       </c>
       <c r="U55" s="1" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>194</v>
+        <v>87</v>
       </c>
       <c r="B56" s="1">
-        <v>6813</v>
+        <v>102542</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="D56" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E56" s="2">
+        <v>45694</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I56" s="1">
+        <v>22</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K56" s="1">
+        <v>160</v>
+      </c>
+      <c r="L56" s="2">
         <v>45722</v>
       </c>
-      <c r="E56" s="2">
+      <c r="M56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O56" s="2">
         <v>45722</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I56" s="1">
-        <v>10</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="K56" s="1">
-        <v>0</v>
-      </c>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
+      <c r="P56" s="2">
+        <v>45694</v>
+      </c>
       <c r="Q56" s="1">
         <v>0</v>
       </c>
       <c r="R56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" s="1"/>
       <c r="T56" s="1">
         <v>0</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="B57" s="1">
-        <v>10053</v>
+        <v>3673</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="D57" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="E57" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>3</v>
+        <v>169</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I57" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>204</v>
+        <v>66</v>
+      </c>
+      <c r="K57" s="1">
+        <v>50</v>
       </c>
       <c r="L57" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>5</v>
@@ -4793,10 +5088,10 @@
         <v>6</v>
       </c>
       <c r="O57" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="P57" s="2">
-        <v>45753</v>
+        <v>45694</v>
       </c>
       <c r="Q57" s="1">
         <v>0</v>
@@ -4809,18 +5104,18 @@
         <v>0</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>205</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="B58" s="1">
-        <v>10052</v>
+        <v>9992</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="D58" s="2">
         <v>45694</v>
@@ -4829,22 +5124,22 @@
         <v>45694</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="I58" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="K58" s="1">
+        <v>50</v>
       </c>
       <c r="L58" s="2">
         <v>45694</v>
@@ -4872,96 +5167,104 @@
         <v>0</v>
       </c>
       <c r="U58" s="1" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="B59" s="1">
-        <v>10054</v>
+        <v>5306</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="D59" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="E59" s="2">
-        <v>45783</v>
+        <v>45814</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>3</v>
+        <v>181</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>210</v>
+        <v>4</v>
       </c>
       <c r="I59" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="K59" s="1">
-        <v>0</v>
-      </c>
-      <c r="L59" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L59" s="2">
+        <v>45814</v>
+      </c>
       <c r="M59" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N59" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
+      <c r="O59" s="2">
+        <v>45814</v>
+      </c>
+      <c r="P59" s="2">
+        <v>45814</v>
+      </c>
       <c r="Q59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" s="1">
-        <v>1</v>
-      </c>
-      <c r="S59" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
+        <v>45814</v>
+      </c>
       <c r="T59" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="B60" s="1">
-        <v>32032</v>
+        <v>5305</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="D60" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="E60" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="I60" s="1">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
@@ -4986,75 +5289,81 @@
         <v>0</v>
       </c>
       <c r="U60" s="1" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="B61" s="1">
-        <v>32033</v>
+        <v>5303</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="D61" s="2">
-        <v>45694</v>
+        <v>45722</v>
       </c>
       <c r="E61" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="I61" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="K61" s="1">
-        <v>0</v>
-      </c>
-      <c r="L61" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L61" s="2">
+        <v>45753</v>
+      </c>
       <c r="M61" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
+      <c r="O61" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P61" s="2">
+        <v>45722</v>
+      </c>
       <c r="Q61" s="1">
         <v>0</v>
       </c>
       <c r="R61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" s="1"/>
       <c r="T61" s="1">
         <v>0</v>
       </c>
       <c r="U61" s="1" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="B62" s="1">
-        <v>32034</v>
+        <v>5301</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D62" s="2">
         <v>45722</v>
@@ -5063,19 +5372,19 @@
         <v>45722</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="I62" s="1">
         <v>10</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -5100,75 +5409,81 @@
         <v>0</v>
       </c>
       <c r="U62" s="1" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="B63" s="1">
-        <v>32038</v>
+        <v>31896</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="D63" s="2">
-        <v>45783</v>
+        <v>45753</v>
       </c>
       <c r="E63" s="2">
-        <v>45783</v>
+        <v>45753</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="I63" s="1">
         <v>10</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>224</v>
+        <v>71</v>
       </c>
       <c r="K63" s="1">
-        <v>0</v>
-      </c>
-      <c r="L63" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L63" s="2">
+        <v>45753</v>
+      </c>
       <c r="M63" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
+      <c r="O63" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P63" s="2">
+        <v>45753</v>
+      </c>
       <c r="Q63" s="1">
         <v>0</v>
       </c>
       <c r="R63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" s="1"/>
       <c r="T63" s="1">
         <v>0</v>
       </c>
       <c r="U63" s="1" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="B64" s="1">
-        <v>32036</v>
+        <v>31897</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="D64" s="2">
         <v>45753</v>
@@ -5177,19 +5492,19 @@
         <v>45753</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="I64" s="1">
         <v>10</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="K64" s="1">
         <v>50</v>
@@ -5220,45 +5535,45 @@
         <v>0</v>
       </c>
       <c r="U64" s="1" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B65" s="1">
-        <v>32035</v>
+        <v>3927</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="D65" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="E65" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="I65" s="1">
         <v>10</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="K65" s="1">
         <v>50</v>
       </c>
       <c r="L65" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>5</v>
@@ -5267,10 +5582,10 @@
         <v>6</v>
       </c>
       <c r="O65" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="P65" s="2">
-        <v>45753</v>
+        <v>45783</v>
       </c>
       <c r="Q65" s="1">
         <v>0</v>
@@ -5283,18 +5598,18 @@
         <v>0</v>
       </c>
       <c r="U65" s="1" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B66" s="1">
-        <v>32037</v>
+        <v>24402</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="D66" s="2">
         <v>45753</v>
@@ -5303,25 +5618,25 @@
         <v>45753</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>114</v>
+        <v>205</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>69</v>
+        <v>206</v>
       </c>
       <c r="I66" s="1">
         <v>10</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="K66" s="1">
         <v>50</v>
       </c>
       <c r="L66" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>5</v>
@@ -5330,7 +5645,7 @@
         <v>6</v>
       </c>
       <c r="O66" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="P66" s="2">
         <v>45753</v>
@@ -5346,99 +5661,105 @@
         <v>0</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="B67" s="1">
-        <v>790</v>
+        <v>26849</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="D67" s="2">
-        <v>45783</v>
+        <v>45694</v>
       </c>
       <c r="E67" s="2">
-        <v>45783</v>
+        <v>45694</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="I67" s="1">
         <v>10</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>238</v>
+        <v>66</v>
       </c>
       <c r="K67" s="1">
-        <v>0</v>
-      </c>
-      <c r="L67" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L67" s="2">
+        <v>45694</v>
+      </c>
       <c r="M67" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
+      <c r="O67" s="2">
+        <v>45694</v>
+      </c>
+      <c r="P67" s="2">
+        <v>45694</v>
+      </c>
       <c r="Q67" s="1">
         <v>0</v>
       </c>
       <c r="R67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" s="1"/>
       <c r="T67" s="1">
         <v>0</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="B68" s="1">
-        <v>11468</v>
+        <v>7299</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="D68" s="2">
-        <v>45694</v>
+        <v>45722</v>
       </c>
       <c r="E68" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>69</v>
+        <v>176</v>
       </c>
       <c r="I68" s="1">
         <v>10</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="K68" s="1">
-        <v>50</v>
+        <v>218</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="L68" s="2">
         <v>45753</v>
@@ -5453,7 +5774,7 @@
         <v>45753</v>
       </c>
       <c r="P68" s="2">
-        <v>45694</v>
+        <v>45722</v>
       </c>
       <c r="Q68" s="1">
         <v>0</v>
@@ -5466,45 +5787,45 @@
         <v>0</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="B69" s="1">
-        <v>11469</v>
+        <v>7298</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="D69" s="2">
-        <v>45694</v>
+        <v>45722</v>
       </c>
       <c r="E69" s="2">
         <v>45722</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="I69" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="K69" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L69" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>5</v>
@@ -5513,61 +5834,63 @@
         <v>6</v>
       </c>
       <c r="O69" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="P69" s="2">
-        <v>45694</v>
+        <v>45938</v>
       </c>
       <c r="Q69" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R69" s="1">
         <v>0</v>
       </c>
-      <c r="S69" s="1"/>
-      <c r="T69" s="1">
-        <v>0</v>
+      <c r="S69" s="2">
+        <v>45722</v>
+      </c>
+      <c r="T69" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="B70" s="1">
-        <v>11467</v>
+        <v>7300</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="D70" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="E70" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="I70" s="1">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="K70" s="1">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="L70" s="2">
-        <v>45722</v>
+        <v>45753</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>5</v>
@@ -5576,10 +5899,10 @@
         <v>6</v>
       </c>
       <c r="O70" s="2">
-        <v>45722</v>
+        <v>45753</v>
       </c>
       <c r="P70" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="Q70" s="1">
         <v>0</v>
@@ -5592,18 +5915,18 @@
         <v>0</v>
       </c>
       <c r="U70" s="1" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="B71" s="1">
-        <v>11472</v>
+        <v>7301</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="D71" s="2">
         <v>45783</v>
@@ -5612,82 +5935,88 @@
         <v>45783</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>255</v>
+        <v>218</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="I71" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K71" s="1">
-        <v>0</v>
-      </c>
-      <c r="L71" s="1"/>
+        <v>218</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="L71" s="2">
+        <v>45783</v>
+      </c>
       <c r="M71" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O71" s="1"/>
-      <c r="P71" s="1"/>
+      <c r="O71" s="2">
+        <v>45783</v>
+      </c>
+      <c r="P71" s="2">
+        <v>45783</v>
+      </c>
       <c r="Q71" s="1">
         <v>0</v>
       </c>
       <c r="R71" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" s="1"/>
       <c r="T71" s="1">
         <v>0</v>
       </c>
       <c r="U71" s="1" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B72" s="1">
-        <v>11470</v>
+        <v>13835</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D72" s="2">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="E72" s="2">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>114</v>
+        <v>205</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>137</v>
+        <v>236</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="I72" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="K72" s="1">
         <v>50</v>
       </c>
       <c r="L72" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>5</v>
@@ -5696,10 +6025,10 @@
         <v>6</v>
       </c>
       <c r="O72" s="2">
-        <v>45753</v>
+        <v>45722</v>
       </c>
       <c r="P72" s="2">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="Q72" s="1">
         <v>0</v>
@@ -5712,156 +6041,168 @@
         <v>0</v>
       </c>
       <c r="U72" s="1" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B73" s="1">
+        <v>13836</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D73" s="2">
+        <v>45722</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45753</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B73" s="1">
-        <v>11471</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D73" s="2">
-        <v>45694</v>
-      </c>
-      <c r="E73" s="2">
-        <v>45753</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="H73" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="I73" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="K73" s="1">
-        <v>0</v>
-      </c>
-      <c r="L73" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L73" s="2">
+        <v>45753</v>
+      </c>
       <c r="M73" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N73" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1"/>
+      <c r="O73" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P73" s="2">
+        <v>45722</v>
+      </c>
       <c r="Q73" s="1">
         <v>0</v>
       </c>
       <c r="R73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" s="1"/>
       <c r="T73" s="1">
         <v>0</v>
       </c>
       <c r="U73" s="1" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="B74" s="1">
-        <v>4810</v>
+        <v>13837</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D74" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="E74" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>114</v>
+        <v>205</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="I74" s="1">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="K74" s="1">
-        <v>0</v>
-      </c>
-      <c r="L74" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="L74" s="2">
+        <v>45814</v>
+      </c>
       <c r="M74" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1"/>
+      <c r="O74" s="2">
+        <v>45814</v>
+      </c>
+      <c r="P74" s="2">
+        <v>45783</v>
+      </c>
       <c r="Q74" s="1">
         <v>0</v>
       </c>
       <c r="R74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" s="1"/>
       <c r="T74" s="1">
         <v>0</v>
       </c>
       <c r="U74" s="1" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="B75" s="1">
-        <v>13309</v>
+        <v>6814</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D75" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="E75" s="2">
-        <v>45722</v>
+        <v>45783</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="I75" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K75" s="1">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L75" s="2">
         <v>45783</v>
@@ -5876,7 +6217,7 @@
         <v>45783</v>
       </c>
       <c r="P75" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="Q75" s="1">
         <v>0</v>
@@ -5889,18 +6230,18 @@
         <v>0</v>
       </c>
       <c r="U75" s="1" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="B76" s="1">
-        <v>13310</v>
+        <v>6813</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D76" s="2">
         <v>45722</v>
@@ -5909,25 +6250,25 @@
         <v>45722</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>272</v>
+        <v>55</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="I76" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>177</v>
+        <v>71</v>
+      </c>
+      <c r="K76" s="1">
+        <v>50</v>
       </c>
       <c r="L76" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>5</v>
@@ -5936,7 +6277,7 @@
         <v>6</v>
       </c>
       <c r="O76" s="2">
-        <v>45753</v>
+        <v>45814</v>
       </c>
       <c r="P76" s="2">
         <v>45722</v>
@@ -5952,18 +6293,18 @@
         <v>0</v>
       </c>
       <c r="U76" s="1" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B77" s="1">
-        <v>13311</v>
+        <v>10054</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="D77" s="2">
         <v>45753</v>
@@ -5972,25 +6313,25 @@
         <v>45783</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>268</v>
+        <v>3</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="I77" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>177</v>
+        <v>257</v>
       </c>
       <c r="L77" s="2">
-        <v>45783</v>
+        <v>45814</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>5</v>
@@ -5999,7 +6340,7 @@
         <v>6</v>
       </c>
       <c r="O77" s="2">
-        <v>45783</v>
+        <v>45814</v>
       </c>
       <c r="P77" s="2">
         <v>45753</v>
@@ -6015,45 +6356,45 @@
         <v>0</v>
       </c>
       <c r="U77" s="1" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B78" s="1">
-        <v>13308</v>
+        <v>10053</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="D78" s="2">
-        <v>45694</v>
+        <v>45753</v>
       </c>
       <c r="E78" s="2">
-        <v>45722</v>
+        <v>45753</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>273</v>
+        <v>3</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="I78" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="K78" s="1">
-        <v>325</v>
+        <v>256</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="L78" s="2">
-        <v>45722</v>
+        <v>45753</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>5</v>
@@ -6062,10 +6403,10 @@
         <v>6</v>
       </c>
       <c r="O78" s="2">
-        <v>45722</v>
-      </c>
-      <c r="P78" s="1" t="s">
-        <v>280</v>
+        <v>45753</v>
+      </c>
+      <c r="P78" s="2">
+        <v>45753</v>
       </c>
       <c r="Q78" s="1">
         <v>0</v>
@@ -6078,45 +6419,45 @@
         <v>0</v>
       </c>
       <c r="U78" s="1" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B79" s="1">
-        <v>13306</v>
+        <v>10057</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="D79" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="E79" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>283</v>
+        <v>3</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="I79" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="K79" s="1">
-        <v>65</v>
+        <v>256</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="L79" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>5</v>
@@ -6125,10 +6466,10 @@
         <v>6</v>
       </c>
       <c r="O79" s="2">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="P79" s="2">
-        <v>45694</v>
+        <v>45783</v>
       </c>
       <c r="Q79" s="1">
         <v>0</v>
@@ -6141,45 +6482,45 @@
         <v>0</v>
       </c>
       <c r="U79" s="1" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B80" s="1">
-        <v>13307</v>
+        <v>10052</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="D80" s="2">
         <v>45694</v>
       </c>
       <c r="E80" s="2">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>268</v>
+        <v>3</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="I80" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K80" s="1">
-        <v>65</v>
+        <v>256</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="L80" s="2">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>5</v>
@@ -6188,7 +6529,7 @@
         <v>6</v>
       </c>
       <c r="O80" s="2">
-        <v>45722</v>
+        <v>45694</v>
       </c>
       <c r="P80" s="2">
         <v>45694</v>
@@ -6204,31 +6545,1890 @@
         <v>0</v>
       </c>
       <c r="U80" s="1" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
+      <c r="A81" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B81" s="1">
+        <v>10056</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D81" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I81" s="1">
+        <v>10</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K81" s="1">
+        <v>0</v>
+      </c>
       <c r="L81" s="1"/>
-      <c r="M81" s="1"/>
-      <c r="N81" s="1"/>
+      <c r="M81" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="O81" s="1"/>
       <c r="P81" s="1"/>
-      <c r="Q81" s="1"/>
-      <c r="R81" s="1"/>
+      <c r="Q81" s="1">
+        <v>0</v>
+      </c>
+      <c r="R81" s="1">
+        <v>1</v>
+      </c>
       <c r="S81" s="1"/>
-      <c r="T81" s="1"/>
-      <c r="U81" s="1"/>
+      <c r="T81" s="1">
+        <v>0</v>
+      </c>
+      <c r="U81" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B82" s="1">
+        <v>10055</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D82" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I82" s="1">
+        <v>10</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K82" s="1">
+        <v>0</v>
+      </c>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1">
+        <v>0</v>
+      </c>
+      <c r="R82" s="1">
+        <v>1</v>
+      </c>
+      <c r="S82" s="1"/>
+      <c r="T82" s="1">
+        <v>0</v>
+      </c>
+      <c r="U82" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B83" s="1">
+        <v>27991</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D83" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I83" s="1">
+        <v>10</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K83" s="1">
+        <v>0</v>
+      </c>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O83" s="1"/>
+      <c r="P83" s="1"/>
+      <c r="Q83" s="1">
+        <v>0</v>
+      </c>
+      <c r="R83" s="1">
+        <v>1</v>
+      </c>
+      <c r="S83" s="1"/>
+      <c r="T83" s="1">
+        <v>0</v>
+      </c>
+      <c r="U83" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B84" s="1">
+        <v>27990</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D84" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I84" s="1">
+        <v>10</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K84" s="1">
+        <v>0</v>
+      </c>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O84" s="1"/>
+      <c r="P84" s="1"/>
+      <c r="Q84" s="1">
+        <v>0</v>
+      </c>
+      <c r="R84" s="1">
+        <v>1</v>
+      </c>
+      <c r="S84" s="1"/>
+      <c r="T84" s="1">
+        <v>0</v>
+      </c>
+      <c r="U84" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B85" s="1">
+        <v>27993</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D85" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I85" s="1">
+        <v>10</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K85" s="1">
+        <v>0</v>
+      </c>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O85" s="1"/>
+      <c r="P85" s="1"/>
+      <c r="Q85" s="1">
+        <v>0</v>
+      </c>
+      <c r="R85" s="1">
+        <v>1</v>
+      </c>
+      <c r="S85" s="1"/>
+      <c r="T85" s="1">
+        <v>0</v>
+      </c>
+      <c r="U85" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B86" s="1">
+        <v>27992</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D86" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I86" s="1">
+        <v>27</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="K86" s="1">
+        <v>0</v>
+      </c>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O86" s="1"/>
+      <c r="P86" s="1"/>
+      <c r="Q86" s="1">
+        <v>0</v>
+      </c>
+      <c r="R86" s="1">
+        <v>1</v>
+      </c>
+      <c r="S86" s="1"/>
+      <c r="T86" s="1">
+        <v>0</v>
+      </c>
+      <c r="U86" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B87" s="1">
+        <v>32032</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D87" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45694</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I87" s="1">
+        <v>21</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K87" s="1">
+        <v>0</v>
+      </c>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O87" s="1"/>
+      <c r="P87" s="1"/>
+      <c r="Q87" s="1">
+        <v>0</v>
+      </c>
+      <c r="R87" s="1">
+        <v>1</v>
+      </c>
+      <c r="S87" s="1"/>
+      <c r="T87" s="1">
+        <v>0</v>
+      </c>
+      <c r="U87" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B88" s="1">
+        <v>32033</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D88" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45694</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I88" s="1">
+        <v>10</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="K88" s="1">
+        <v>0</v>
+      </c>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O88" s="1"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1">
+        <v>0</v>
+      </c>
+      <c r="R88" s="1">
+        <v>1</v>
+      </c>
+      <c r="S88" s="1"/>
+      <c r="T88" s="1">
+        <v>0</v>
+      </c>
+      <c r="U88" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B89" s="1">
+        <v>32034</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D89" s="2">
+        <v>45722</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45722</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I89" s="1">
+        <v>10</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K89" s="1">
+        <v>0</v>
+      </c>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O89" s="1"/>
+      <c r="P89" s="1"/>
+      <c r="Q89" s="1">
+        <v>0</v>
+      </c>
+      <c r="R89" s="1">
+        <v>1</v>
+      </c>
+      <c r="S89" s="1"/>
+      <c r="T89" s="1">
+        <v>0</v>
+      </c>
+      <c r="U89" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B90" s="1">
+        <v>32038</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D90" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45783</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I90" s="1">
+        <v>10</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="K90" s="1">
+        <v>0</v>
+      </c>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O90" s="1"/>
+      <c r="P90" s="1"/>
+      <c r="Q90" s="1">
+        <v>0</v>
+      </c>
+      <c r="R90" s="1">
+        <v>1</v>
+      </c>
+      <c r="S90" s="1"/>
+      <c r="T90" s="1">
+        <v>0</v>
+      </c>
+      <c r="U90" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B91" s="1">
+        <v>32039</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D91" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I91" s="1">
+        <v>10</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="K91" s="1">
+        <v>0</v>
+      </c>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1">
+        <v>0</v>
+      </c>
+      <c r="R91" s="1">
+        <v>1</v>
+      </c>
+      <c r="S91" s="1"/>
+      <c r="T91" s="1">
+        <v>0</v>
+      </c>
+      <c r="U91" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B92" s="1">
+        <v>32036</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D92" s="2">
+        <v>45753</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45753</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I92" s="1">
+        <v>10</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K92" s="1">
+        <v>50</v>
+      </c>
+      <c r="L92" s="2">
+        <v>45753</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O92" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P92" s="2">
+        <v>45753</v>
+      </c>
+      <c r="Q92" s="1">
+        <v>0</v>
+      </c>
+      <c r="R92" s="1">
+        <v>0</v>
+      </c>
+      <c r="S92" s="1"/>
+      <c r="T92" s="1">
+        <v>0</v>
+      </c>
+      <c r="U92" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B93" s="1">
+        <v>32035</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D93" s="2">
+        <v>45753</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45753</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I93" s="1">
+        <v>10</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K93" s="1">
+        <v>50</v>
+      </c>
+      <c r="L93" s="2">
+        <v>45753</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O93" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P93" s="2">
+        <v>45753</v>
+      </c>
+      <c r="Q93" s="1">
+        <v>0</v>
+      </c>
+      <c r="R93" s="1">
+        <v>0</v>
+      </c>
+      <c r="S93" s="1"/>
+      <c r="T93" s="1">
+        <v>0</v>
+      </c>
+      <c r="U93" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B94" s="1">
+        <v>32037</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D94" s="2">
+        <v>45753</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45753</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I94" s="1">
+        <v>10</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="K94" s="1">
+        <v>50</v>
+      </c>
+      <c r="L94" s="2">
+        <v>45753</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O94" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P94" s="2">
+        <v>45753</v>
+      </c>
+      <c r="Q94" s="1">
+        <v>0</v>
+      </c>
+      <c r="R94" s="1">
+        <v>0</v>
+      </c>
+      <c r="S94" s="1"/>
+      <c r="T94" s="1">
+        <v>0</v>
+      </c>
+      <c r="U94" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B95" s="1">
+        <v>790</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D95" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45783</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I95" s="1">
+        <v>10</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="K95" s="1">
+        <v>0</v>
+      </c>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O95" s="1"/>
+      <c r="P95" s="1"/>
+      <c r="Q95" s="1">
+        <v>0</v>
+      </c>
+      <c r="R95" s="1">
+        <v>1</v>
+      </c>
+      <c r="S95" s="1"/>
+      <c r="T95" s="1">
+        <v>0</v>
+      </c>
+      <c r="U95" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B96" s="1">
+        <v>791</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D96" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I96" s="1">
+        <v>25</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="K96" s="1">
+        <v>0</v>
+      </c>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O96" s="1"/>
+      <c r="P96" s="1"/>
+      <c r="Q96" s="1">
+        <v>0</v>
+      </c>
+      <c r="R96" s="1">
+        <v>1</v>
+      </c>
+      <c r="S96" s="1"/>
+      <c r="T96" s="1">
+        <v>0</v>
+      </c>
+      <c r="U96" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B97" s="1">
+        <v>11468</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D97" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45694</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I97" s="1">
+        <v>10</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K97" s="1">
+        <v>50</v>
+      </c>
+      <c r="L97" s="2">
+        <v>45753</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O97" s="2">
+        <v>45783</v>
+      </c>
+      <c r="P97" s="2">
+        <v>45937</v>
+      </c>
+      <c r="Q97" s="1">
+        <v>1</v>
+      </c>
+      <c r="R97" s="1">
+        <v>0</v>
+      </c>
+      <c r="S97" s="2">
+        <v>45783</v>
+      </c>
+      <c r="T97" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="U97" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B98" s="1">
+        <v>11469</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D98" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45722</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I98" s="1">
+        <v>5</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="K98" s="1">
+        <v>50</v>
+      </c>
+      <c r="L98" s="2">
+        <v>45753</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O98" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P98" s="2">
+        <v>45694</v>
+      </c>
+      <c r="Q98" s="1">
+        <v>0</v>
+      </c>
+      <c r="R98" s="1">
+        <v>0</v>
+      </c>
+      <c r="S98" s="1"/>
+      <c r="T98" s="1">
+        <v>0</v>
+      </c>
+      <c r="U98" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B99" s="1">
+        <v>11467</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D99" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45694</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I99" s="1">
+        <v>27</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="K99" s="1">
+        <v>41</v>
+      </c>
+      <c r="L99" s="2">
+        <v>45722</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O99" s="2">
+        <v>45722</v>
+      </c>
+      <c r="P99" s="2">
+        <v>45694</v>
+      </c>
+      <c r="Q99" s="1">
+        <v>0</v>
+      </c>
+      <c r="R99" s="1">
+        <v>0</v>
+      </c>
+      <c r="S99" s="1"/>
+      <c r="T99" s="1">
+        <v>0</v>
+      </c>
+      <c r="U99" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B100" s="1">
+        <v>11472</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D100" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45783</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I100" s="1">
+        <v>10</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K100" s="1">
+        <v>0</v>
+      </c>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O100" s="1"/>
+      <c r="P100" s="1"/>
+      <c r="Q100" s="1">
+        <v>0</v>
+      </c>
+      <c r="R100" s="1">
+        <v>1</v>
+      </c>
+      <c r="S100" s="1"/>
+      <c r="T100" s="1">
+        <v>0</v>
+      </c>
+      <c r="U100" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B101" s="1">
+        <v>11470</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D101" s="2">
+        <v>45722</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45722</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I101" s="1">
+        <v>5</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="K101" s="1">
+        <v>50</v>
+      </c>
+      <c r="L101" s="2">
+        <v>45753</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O101" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P101" s="2">
+        <v>45722</v>
+      </c>
+      <c r="Q101" s="1">
+        <v>0</v>
+      </c>
+      <c r="R101" s="1">
+        <v>0</v>
+      </c>
+      <c r="S101" s="1"/>
+      <c r="T101" s="1">
+        <v>0</v>
+      </c>
+      <c r="U101" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B102" s="1">
+        <v>11473</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D102" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45783</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I102" s="1">
+        <v>10</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="K102" s="1">
+        <v>0</v>
+      </c>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O102" s="1"/>
+      <c r="P102" s="1"/>
+      <c r="Q102" s="1">
+        <v>0</v>
+      </c>
+      <c r="R102" s="1">
+        <v>1</v>
+      </c>
+      <c r="S102" s="1"/>
+      <c r="T102" s="1">
+        <v>0</v>
+      </c>
+      <c r="U102" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B103" s="1">
+        <v>11471</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D103" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45753</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I103" s="1">
+        <v>12</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="K103" s="1">
+        <v>0</v>
+      </c>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O103" s="1"/>
+      <c r="P103" s="1"/>
+      <c r="Q103" s="1">
+        <v>0</v>
+      </c>
+      <c r="R103" s="1">
+        <v>1</v>
+      </c>
+      <c r="S103" s="1"/>
+      <c r="T103" s="1">
+        <v>0</v>
+      </c>
+      <c r="U103" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B104" s="1">
+        <v>4810</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D104" s="2">
+        <v>45722</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45753</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I104" s="1">
+        <v>5</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="K104" s="1">
+        <v>50</v>
+      </c>
+      <c r="L104" s="2">
+        <v>45814</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O104" s="2">
+        <v>45814</v>
+      </c>
+      <c r="P104" s="2">
+        <v>45722</v>
+      </c>
+      <c r="Q104" s="1">
+        <v>0</v>
+      </c>
+      <c r="R104" s="1">
+        <v>0</v>
+      </c>
+      <c r="S104" s="1"/>
+      <c r="T104" s="1">
+        <v>0</v>
+      </c>
+      <c r="U104" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B105" s="1">
+        <v>13309</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D105" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45722</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I105" s="1">
+        <v>10</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K105" s="1">
+        <v>65</v>
+      </c>
+      <c r="L105" s="2">
+        <v>45783</v>
+      </c>
+      <c r="M105" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O105" s="2">
+        <v>45783</v>
+      </c>
+      <c r="P105" s="2">
+        <v>45694</v>
+      </c>
+      <c r="Q105" s="1">
+        <v>0</v>
+      </c>
+      <c r="R105" s="1">
+        <v>0</v>
+      </c>
+      <c r="S105" s="1"/>
+      <c r="T105" s="1">
+        <v>0</v>
+      </c>
+      <c r="U105" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B106" s="1">
+        <v>13310</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D106" s="2">
+        <v>45722</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45722</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="I106" s="1">
+        <v>6</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="L106" s="2">
+        <v>45753</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O106" s="2">
+        <v>45753</v>
+      </c>
+      <c r="P106" s="2">
+        <v>45722</v>
+      </c>
+      <c r="Q106" s="1">
+        <v>0</v>
+      </c>
+      <c r="R106" s="1">
+        <v>0</v>
+      </c>
+      <c r="S106" s="1"/>
+      <c r="T106" s="1">
+        <v>0</v>
+      </c>
+      <c r="U106" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B107" s="1">
+        <v>13311</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D107" s="2">
+        <v>45753</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45783</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="I107" s="1">
+        <v>15</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="L107" s="2">
+        <v>45783</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O107" s="2">
+        <v>45783</v>
+      </c>
+      <c r="P107" s="2">
+        <v>45753</v>
+      </c>
+      <c r="Q107" s="1">
+        <v>0</v>
+      </c>
+      <c r="R107" s="1">
+        <v>0</v>
+      </c>
+      <c r="S107" s="1"/>
+      <c r="T107" s="1">
+        <v>0</v>
+      </c>
+      <c r="U107" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B108" s="1">
+        <v>13308</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D108" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45722</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I108" s="1">
+        <v>15</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K108" s="1">
+        <v>325</v>
+      </c>
+      <c r="L108" s="2">
+        <v>45722</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O108" s="2">
+        <v>45722</v>
+      </c>
+      <c r="P108" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q108" s="1">
+        <v>0</v>
+      </c>
+      <c r="R108" s="1">
+        <v>0</v>
+      </c>
+      <c r="S108" s="1"/>
+      <c r="T108" s="1">
+        <v>0</v>
+      </c>
+      <c r="U108" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B109" s="1">
+        <v>13306</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D109" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45722</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I109" s="1">
+        <v>12</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="K109" s="1">
+        <v>65</v>
+      </c>
+      <c r="L109" s="2">
+        <v>45722</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O109" s="2">
+        <v>45722</v>
+      </c>
+      <c r="P109" s="2">
+        <v>45694</v>
+      </c>
+      <c r="Q109" s="1">
+        <v>0</v>
+      </c>
+      <c r="R109" s="1">
+        <v>0</v>
+      </c>
+      <c r="S109" s="1"/>
+      <c r="T109" s="1">
+        <v>0</v>
+      </c>
+      <c r="U109" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B110" s="1">
+        <v>13307</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D110" s="2">
+        <v>45694</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45722</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I110" s="1">
+        <v>5</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K110" s="1">
+        <v>65</v>
+      </c>
+      <c r="L110" s="2">
+        <v>45722</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O110" s="2">
+        <v>45722</v>
+      </c>
+      <c r="P110" s="2">
+        <v>45694</v>
+      </c>
+      <c r="Q110" s="1">
+        <v>0</v>
+      </c>
+      <c r="R110" s="1">
+        <v>0</v>
+      </c>
+      <c r="S110" s="1"/>
+      <c r="T110" s="1">
+        <v>0</v>
+      </c>
+      <c r="U110" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B111" s="1">
+        <v>13312</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D111" s="2">
+        <v>45783</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45814</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I111" s="1">
+        <v>20</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K111" s="1">
+        <v>65</v>
+      </c>
+      <c r="L111" s="2">
+        <v>45814</v>
+      </c>
+      <c r="M111" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N111" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O111" s="2">
+        <v>45814</v>
+      </c>
+      <c r="P111" s="2">
+        <v>45783</v>
+      </c>
+      <c r="Q111" s="1">
+        <v>0</v>
+      </c>
+      <c r="R111" s="1">
+        <v>0</v>
+      </c>
+      <c r="S111" s="1"/>
+      <c r="T111" s="1">
+        <v>0</v>
+      </c>
+      <c r="U111" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1"/>
+      <c r="N112" s="1"/>
+      <c r="O112" s="1"/>
+      <c r="P112" s="1"/>
+      <c r="Q112" s="1"/>
+      <c r="R112" s="1"/>
+      <c r="S112" s="1"/>
+      <c r="T112" s="1"/>
+      <c r="U112" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -6236,7 +8436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB7C351-98C3-4E9F-BCD3-AEF8A1E1C34D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BCF7C1-28CC-4A37-9837-2BC9C07D6339}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
